--- a/artfynd/A 20061-2026 artfynd.xlsx
+++ b/artfynd/A 20061-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136329777</v>
       </c>
       <c r="B2" t="n">
-        <v>92373</v>
+        <v>92376</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136329783</v>
       </c>
       <c r="B3" t="n">
-        <v>92113</v>
+        <v>92116</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136329775</v>
       </c>
       <c r="B4" t="n">
-        <v>92534</v>
+        <v>92537</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>136329782</v>
       </c>
       <c r="B10" t="n">
-        <v>98204</v>
+        <v>98207</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 20061-2026 artfynd.xlsx
+++ b/artfynd/A 20061-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136329777</v>
       </c>
       <c r="B2" t="n">
-        <v>92376</v>
+        <v>92377</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136329783</v>
       </c>
       <c r="B3" t="n">
-        <v>92116</v>
+        <v>92117</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136329775</v>
       </c>
       <c r="B4" t="n">
-        <v>92537</v>
+        <v>92538</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>136329782</v>
       </c>
       <c r="B10" t="n">
-        <v>98207</v>
+        <v>98208</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 20061-2026 artfynd.xlsx
+++ b/artfynd/A 20061-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136329777</v>
       </c>
       <c r="B2" t="n">
-        <v>92377</v>
+        <v>92382</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136329783</v>
       </c>
       <c r="B3" t="n">
-        <v>92117</v>
+        <v>92122</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136329775</v>
       </c>
       <c r="B4" t="n">
-        <v>92538</v>
+        <v>92543</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136329785</v>
       </c>
       <c r="B5" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>136329779</v>
       </c>
       <c r="B6" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>136329780</v>
       </c>
       <c r="B7" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>136329784</v>
       </c>
       <c r="B8" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>136329782</v>
       </c>
       <c r="B10" t="n">
-        <v>98208</v>
+        <v>98213</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 20061-2026 artfynd.xlsx
+++ b/artfynd/A 20061-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136329777</v>
       </c>
       <c r="B2" t="n">
-        <v>92382</v>
+        <v>92384</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136329783</v>
       </c>
       <c r="B3" t="n">
-        <v>92122</v>
+        <v>92124</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136329775</v>
       </c>
       <c r="B4" t="n">
-        <v>92543</v>
+        <v>92545</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>136329782</v>
       </c>
       <c r="B10" t="n">
-        <v>98213</v>
+        <v>98215</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 20061-2026 artfynd.xlsx
+++ b/artfynd/A 20061-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136329777</v>
       </c>
       <c r="B2" t="n">
-        <v>92384</v>
+        <v>92386</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136329783</v>
       </c>
       <c r="B3" t="n">
-        <v>92124</v>
+        <v>92126</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136329775</v>
       </c>
       <c r="B4" t="n">
-        <v>92545</v>
+        <v>92547</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>136329782</v>
       </c>
       <c r="B10" t="n">
-        <v>98215</v>
+        <v>98221</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
